--- a/public/static/成品(没有型号)导入模板.xlsx
+++ b/public/static/成品(没有型号)导入模板.xlsx
@@ -28,9 +28,31 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>序号</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>产品分类</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
   </si>
   <si>
     <t>产品编码</t>
@@ -1530,25 +1552,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
-    <col min="2" max="2" width="18.225" customWidth="1"/>
-    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.225" customWidth="1"/>
-    <col min="6" max="6" width="15.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="17.225" customWidth="1"/>
-    <col min="8" max="10" width="16.4416666666667" customWidth="1"/>
-    <col min="11" max="11" width="16.8916666666667" customWidth="1"/>
-    <col min="12" max="12" width="19.4416666666667" customWidth="1"/>
-    <col min="13" max="13" width="21.5583333333333" customWidth="1"/>
-    <col min="14" max="14" width="19.4416666666667" customWidth="1"/>
-    <col min="15" max="15" width="19" customWidth="1"/>
+    <col min="2" max="3" width="18.225" customWidth="1"/>
+    <col min="4" max="4" width="23.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="17.5583333333333" customWidth="1"/>
+    <col min="6" max="6" width="15.225" customWidth="1"/>
+    <col min="7" max="7" width="15.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="17.225" customWidth="1"/>
+    <col min="9" max="11" width="16.4416666666667" customWidth="1"/>
+    <col min="12" max="12" width="16.8916666666667" customWidth="1"/>
+    <col min="13" max="13" width="19.4416666666667" customWidth="1"/>
+    <col min="14" max="14" width="21.5583333333333" customWidth="1"/>
+    <col min="15" max="15" width="19.4416666666667" customWidth="1"/>
+    <col min="16" max="16" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:15">
+    <row r="1" ht="25" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1588,35 +1610,39 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:15">
+    <row r="2" ht="20" customHeight="1" spans="1:16">
       <c r="A2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="7" t="s">
-        <v>16</v>
-      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="7"/>
+      <c r="J2" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="K2" s="7"/>
-      <c r="L2" s="4"/>
+      <c r="L2" s="7"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
     </row>
     <row r="3" ht="20" customHeight="1"/>
     <row r="4" ht="20" customHeight="1"/>
@@ -1666,13 +1692,13 @@
     <row r="48" ht="20" customHeight="1"/>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2">
       <formula1>"乘,除"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2">
       <formula1>"组装,生产,采购,外协"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:M2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:N2">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1692,42 +1718,42 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="43" customHeight="1" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1"/>

--- a/public/static/成品(没有型号)导入模板.xlsx
+++ b/public/static/成品(没有型号)导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="成品导入模板" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>序号</t>
   </si>
@@ -299,6 +299,12 @@
   </si>
   <si>
     <t>如果是贸易件时，密封盖-结构、密封盖-打字、结构类型、游隙、钢球厂家、油脂、油脂量、噪音、保持架、振动等级、精度等级、颜色、孔径等都非必填，然后产品来源固定死采购</t>
+  </si>
+  <si>
+    <t>产品分类：填写产品分类编码</t>
+  </si>
+  <si>
+    <t>工艺路线：填写工艺路线编码</t>
   </si>
 </sst>
 </file>
@@ -1756,8 +1762,16 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1"/>
-    <row r="10" ht="28" customHeight="1"/>
+    <row r="9" ht="28" customHeight="1" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="11" ht="28" customHeight="1"/>
     <row r="12" ht="28" customHeight="1"/>
     <row r="13" ht="28" customHeight="1"/>
